--- a/model_scheduleSource.xlsx
+++ b/model_scheduleSource.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a034e438f726db5/Documentos/GitHub/TheSimuLeanProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\63391\Desktop\Trabajo\__github\Jaime\TheSimuLeanProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74357CA-EFF6-4587-9069-4DA4D2A5F07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AA831D-4866-41B3-A80C-36860FAE2914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-72" windowWidth="23256" windowHeight="12456" xr2:uid="{A34F26A0-950C-4EF8-94B0-1F4CA0DEB41A}"/>
+    <workbookView xWindow="34980" yWindow="855" windowWidth="21600" windowHeight="11295" xr2:uid="{A34F26A0-950C-4EF8-94B0-1F4CA0DEB41A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
   <si>
     <t>A</t>
   </si>
@@ -62,7 +62,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>Plancha</t>
+    <t>Refuerzo</t>
   </si>
 </sst>
 </file>
@@ -516,9 +516,121 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>3</v>
       </c>
     </row>
